--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2198" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="669">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -334,1650 +334,1635 @@
     <t>SEC-TEST-042</t>
   </si>
   <si>
-    <t>Detect Rate Limiting payload execution against /api/auth/login (Variant 42)</t>
+    <t>Detect Broken Authentication payload execution against /api/generate (Variant 42)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-043</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/user (Variant 43)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-044</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/health (Variant 44)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-045</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/login (Variant 45)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-046</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/quiz (Variant 46)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-047</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/generate (Variant 47)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-048</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/user (Variant 48)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-049</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/health (Variant 49)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-050</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/login (Variant 50)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-051</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/quiz (Variant 51)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-052</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/generate (Variant 52)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-053</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/user (Variant 53)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-054</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/health (Variant 54)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-055</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/login (Variant 55)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-056</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/quiz (Variant 56)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-057</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/generate (Variant 57)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-058</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/user (Variant 58)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-059</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/health (Variant 59)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-060</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/login (Variant 60)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-061</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 61)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-062</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/generate (Variant 62)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-063</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/user (Variant 63)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-064</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/health (Variant 64)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-065</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/login (Variant 65)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-066</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 66)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-067</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/generate (Variant 67)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-068</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/user (Variant 68)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-069</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/health (Variant 69)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-070</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/login (Variant 70)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-071</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 71)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-072</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/generate (Variant 72)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-073</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/user (Variant 73)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-074</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/health (Variant 74)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-075</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/login (Variant 75)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-076</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 76)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-077</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/generate (Variant 77)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-078</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/user (Variant 78)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-079</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/health (Variant 79)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-080</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/login (Variant 80)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-081</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/quiz (Variant 81)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-082</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/generate (Variant 82)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-083</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/user (Variant 83)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-084</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/health (Variant 84)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-085</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/login (Variant 85)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-086</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/quiz (Variant 86)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-087</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/generate (Variant 87)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-088</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/user (Variant 88)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-089</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/health (Variant 89)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-090</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/login (Variant 90)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-091</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/quiz (Variant 91)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-092</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/generate (Variant 92)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-093</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/user (Variant 93)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-094</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/health (Variant 94)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-095</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/login (Variant 95)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-096</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/quiz (Variant 96)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-097</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/generate (Variant 97)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-098</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/user (Variant 98)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-099</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/health (Variant 99)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-100</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/login (Variant 100)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-101</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 101)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-102</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/generate (Variant 102)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-103</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/user (Variant 103)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-104</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/health (Variant 104)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-105</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/login (Variant 105)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-106</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 106)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-107</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/generate (Variant 107)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-108</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/user (Variant 108)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-109</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/health (Variant 109)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-110</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/login (Variant 110)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-111</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 111)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-112</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/generate (Variant 112)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-113</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/user (Variant 113)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-114</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/health (Variant 114)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-115</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/login (Variant 115)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-116</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 116)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-117</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/generate (Variant 117)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-118</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/user (Variant 118)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-119</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/health (Variant 119)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-120</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/login (Variant 120)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-121</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/quiz (Variant 121)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-122</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/generate (Variant 122)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-123</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/user (Variant 123)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-124</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/health (Variant 124)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-125</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/login (Variant 125)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-126</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/quiz (Variant 126)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-127</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/generate (Variant 127)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-128</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/user (Variant 128)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-129</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/health (Variant 129)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-130</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/login (Variant 130)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-131</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/quiz (Variant 131)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-132</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/generate (Variant 132)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-133</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/user (Variant 133)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-134</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/health (Variant 134)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-135</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/login (Variant 135)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-136</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/quiz (Variant 136)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-137</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/generate (Variant 137)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-138</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/user (Variant 138)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-139</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/health (Variant 139)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-140</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/login (Variant 140)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-141</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 141)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-142</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/generate (Variant 142)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-143</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/user (Variant 143)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-144</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/health (Variant 144)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-145</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/login (Variant 145)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-146</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 146)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-147</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/generate (Variant 147)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-148</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/user (Variant 148)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-149</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/health (Variant 149)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-150</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/login (Variant 150)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-151</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 151)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-152</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/generate (Variant 152)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-153</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/user (Variant 153)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-154</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/health (Variant 154)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-155</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/login (Variant 155)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-156</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 156)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-157</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/generate (Variant 157)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-158</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/user (Variant 158)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-159</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/health (Variant 159)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-160</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/login (Variant 160)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-161</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/quiz (Variant 161)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-162</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/generate (Variant 162)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-163</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/user (Variant 163)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-164</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/health (Variant 164)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-165</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/login (Variant 165)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-166</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/quiz (Variant 166)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-167</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/generate (Variant 167)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-168</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/user (Variant 168)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-169</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/health (Variant 169)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-170</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/login (Variant 170)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-171</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/quiz (Variant 171)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-172</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/generate (Variant 172)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-173</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/user (Variant 173)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-174</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/health (Variant 174)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-175</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/login (Variant 175)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-176</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/quiz (Variant 176)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-177</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/generate (Variant 177)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-178</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/user (Variant 178)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-179</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/health (Variant 179)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-180</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/login (Variant 180)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-181</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 181)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-182</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/generate (Variant 182)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-183</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/user (Variant 183)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-184</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/health (Variant 184)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-185</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/login (Variant 185)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-186</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 186)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-187</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/generate (Variant 187)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-188</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/user (Variant 188)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-189</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/health (Variant 189)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-190</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/login (Variant 190)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-191</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 191)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-192</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/generate (Variant 192)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-193</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/user (Variant 193)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-194</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/health (Variant 194)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-195</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/login (Variant 195)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-196</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 196)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-197</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/generate (Variant 197)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-198</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/user (Variant 198)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-199</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/health (Variant 199)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-200</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/login (Variant 200)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-201</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/quiz (Variant 201)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-202</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/generate (Variant 202)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-203</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/user (Variant 203)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-204</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/health (Variant 204)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-205</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/login (Variant 205)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-206</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/quiz (Variant 206)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-207</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/generate (Variant 207)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-208</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/user (Variant 208)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-209</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/health (Variant 209)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-210</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/login (Variant 210)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-211</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/quiz (Variant 211)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-212</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/generate (Variant 212)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-213</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/user (Variant 213)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-214</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/health (Variant 214)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-215</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/login (Variant 215)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-216</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/quiz (Variant 216)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-217</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/generate (Variant 217)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-218</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/user (Variant 218)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-219</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/health (Variant 219)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-220</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/login (Variant 220)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-221</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 221)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-222</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/generate (Variant 222)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-223</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/user (Variant 223)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-224</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/health (Variant 224)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-225</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/login (Variant 225)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-226</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 226)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-227</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/generate (Variant 227)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-228</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/user (Variant 228)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-229</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/health (Variant 229)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-230</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/login (Variant 230)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-231</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 231)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-232</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/generate (Variant 232)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-233</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/user (Variant 233)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-234</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/health (Variant 234)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-235</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/login (Variant 235)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-236</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 236)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-237</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/generate (Variant 237)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-238</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/user (Variant 238)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-239</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/health (Variant 239)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-240</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/login (Variant 240)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-241</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/quiz (Variant 241)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-242</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/generate (Variant 242)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-243</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/user (Variant 243)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-244</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/health (Variant 244)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-245</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/login (Variant 245)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-246</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/quiz (Variant 246)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-247</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/generate (Variant 247)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-248</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/user (Variant 248)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-249</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/health (Variant 249)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-250</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/login (Variant 250)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-251</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/quiz (Variant 251)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-252</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/generate (Variant 252)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-253</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/user (Variant 253)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-254</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/health (Variant 254)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-255</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/login (Variant 255)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-256</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/quiz (Variant 256)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-257</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/generate (Variant 257)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-258</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/user (Variant 258)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-259</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/health (Variant 259)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-260</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/login (Variant 260)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-261</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 261)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-262</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/generate (Variant 262)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-263</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/user (Variant 263)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-264</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/health (Variant 264)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-265</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/login (Variant 265)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-266</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 266)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-267</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/generate (Variant 267)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-268</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/user (Variant 268)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-269</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/health (Variant 269)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-270</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/login (Variant 270)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-271</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 271)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-272</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/generate (Variant 272)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-273</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/user (Variant 273)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-274</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/health (Variant 274)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-275</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/login (Variant 275)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-276</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 276)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-277</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/generate (Variant 277)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-278</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/user (Variant 278)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-279</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/health (Variant 279)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-280</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/login (Variant 280)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-281</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/quiz (Variant 281)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-282</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/generate (Variant 282)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-283</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/user (Variant 283)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-284</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/health (Variant 284)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-285</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/login (Variant 285)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-286</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/quiz (Variant 286)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-287</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/generate (Variant 287)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-288</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/user (Variant 288)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-289</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/health (Variant 289)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-290</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/login (Variant 290)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-291</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/quiz (Variant 291)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-292</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/generate (Variant 292)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-293</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/user (Variant 293)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-294</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/health (Variant 294)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-295</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/login (Variant 295)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-296</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/quiz (Variant 296)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-297</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/generate (Variant 297)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-298</t>
+  </si>
+  <si>
+    <t>Detect Broken Authentication payload execution against /api/user (Variant 298)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-299</t>
+  </si>
+  <si>
+    <t>Detect IDOR payload execution against /api/health (Variant 299)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-300</t>
+  </si>
+  <si>
+    <t>Detect JWT Tampering payload execution against /api/login (Variant 300)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-301</t>
+  </si>
+  <si>
+    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 301)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-302</t>
+  </si>
+  <si>
+    <t>Detect CORS payload execution against /api/generate (Variant 302)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-303</t>
+  </si>
+  <si>
+    <t>Detect Mass Assignment payload execution against /api/user (Variant 303)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-304</t>
+  </si>
+  <si>
+    <t>Detect SQL Injection payload execution against /api/health (Variant 304)</t>
+  </si>
+  <si>
+    <t>SEC-TEST-305</t>
+  </si>
+  <si>
+    <t>Detect XSS payload execution against /api/login (Variant 305)</t>
+  </si>
+  <si>
+    <t>Endpoint</t>
+  </si>
+  <si>
+    <t>HTTP Method</t>
+  </si>
+  <si>
+    <t>Authentication Required</t>
+  </si>
+  <si>
+    <t>Expected Roles</t>
+  </si>
+  <si>
+    <t>Controller/File Path</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>src/routes/health.ts</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>User, Admin</t>
+  </si>
+  <si>
+    <t>src/routes/generate.ts</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>src/routes/quiz.ts</t>
   </si>
   <si>
     <t>/api/auth/login</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Implement strict validation and headers</t>
-  </si>
-  <si>
-    <t>SEC-TEST-043</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/user (Variant 43)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-044</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/health (Variant 44)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-045</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/login (Variant 45)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-046</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/quiz (Variant 46)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-047</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/generate (Variant 47)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-048</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/user (Variant 48)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-049</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/health (Variant 49)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-050</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/login (Variant 50)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-051</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/quiz (Variant 51)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-052</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/generate (Variant 52)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-053</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/user (Variant 53)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-054</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/health (Variant 54)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-055</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/login (Variant 55)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-056</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/quiz (Variant 56)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-057</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/generate (Variant 57)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-058</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/user (Variant 58)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-059</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/health (Variant 59)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-060</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/login (Variant 60)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-061</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 61)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-062</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/generate (Variant 62)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-063</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/user (Variant 63)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-064</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/health (Variant 64)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-065</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/login (Variant 65)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-066</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 66)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-067</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/generate (Variant 67)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-068</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/user (Variant 68)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-069</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/health (Variant 69)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-070</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/login (Variant 70)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-071</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 71)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-072</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/generate (Variant 72)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-073</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/user (Variant 73)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-074</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/health (Variant 74)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-075</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/login (Variant 75)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-076</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 76)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-077</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/generate (Variant 77)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-078</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/user (Variant 78)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-079</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/health (Variant 79)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-080</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/login (Variant 80)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-081</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/quiz (Variant 81)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-082</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/generate (Variant 82)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-083</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/user (Variant 83)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-084</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/health (Variant 84)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-085</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/login (Variant 85)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-086</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/quiz (Variant 86)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-087</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/generate (Variant 87)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-088</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/user (Variant 88)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-089</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/health (Variant 89)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-090</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/login (Variant 90)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-091</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/quiz (Variant 91)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-092</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/generate (Variant 92)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-093</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/user (Variant 93)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-094</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/health (Variant 94)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-095</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/login (Variant 95)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-096</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/quiz (Variant 96)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-097</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/generate (Variant 97)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-098</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/user (Variant 98)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-099</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/health (Variant 99)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-100</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/login (Variant 100)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-101</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 101)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-102</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/generate (Variant 102)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-103</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/user (Variant 103)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-104</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/health (Variant 104)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-105</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/login (Variant 105)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-106</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 106)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-107</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/generate (Variant 107)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-108</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/user (Variant 108)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-109</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/health (Variant 109)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-110</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/login (Variant 110)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-111</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 111)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-112</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/generate (Variant 112)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-113</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against Global Middleware (Variant 113)</t>
-  </si>
-  <si>
-    <t>Global Middleware</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>SEC-TEST-114</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/health (Variant 114)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-115</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/login (Variant 115)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-116</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 116)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-117</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/generate (Variant 117)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-118</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/user (Variant 118)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-119</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/health (Variant 119)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-120</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/login (Variant 120)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-121</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/quiz (Variant 121)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-122</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/generate (Variant 122)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-123</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/user (Variant 123)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-124</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/health (Variant 124)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-125</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/login (Variant 125)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-126</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/quiz (Variant 126)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-127</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/generate (Variant 127)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-128</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/user (Variant 128)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-129</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/health (Variant 129)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-130</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/login (Variant 130)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-131</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/quiz (Variant 131)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-132</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/generate (Variant 132)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-133</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/user (Variant 133)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-134</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/health (Variant 134)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-135</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/login (Variant 135)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-136</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/quiz (Variant 136)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-137</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/generate (Variant 137)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-138</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/user (Variant 138)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-139</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/health (Variant 139)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-140</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/login (Variant 140)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-141</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 141)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-142</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/generate (Variant 142)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-143</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/user (Variant 143)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-144</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/health (Variant 144)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-145</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/login (Variant 145)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-146</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 146)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-147</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/generate (Variant 147)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-148</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/user (Variant 148)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-149</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/health (Variant 149)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-150</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/login (Variant 150)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-151</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 151)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-152</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/generate (Variant 152)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-153</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/user (Variant 153)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-154</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/health (Variant 154)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-155</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/login (Variant 155)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-156</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 156)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-157</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/generate (Variant 157)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-158</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/user (Variant 158)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-159</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/health (Variant 159)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-160</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/login (Variant 160)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-161</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/quiz (Variant 161)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-162</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/generate (Variant 162)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-163</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/user (Variant 163)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-164</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/health (Variant 164)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-165</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/login (Variant 165)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-166</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/quiz (Variant 166)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-167</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/generate (Variant 167)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-168</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/user (Variant 168)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-169</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/health (Variant 169)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-170</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/login (Variant 170)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-171</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/quiz (Variant 171)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-172</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/generate (Variant 172)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-173</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/user (Variant 173)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-174</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/health (Variant 174)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-175</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/login (Variant 175)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-176</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/quiz (Variant 176)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-177</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/generate (Variant 177)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-178</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/user (Variant 178)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-179</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/health (Variant 179)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-180</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/login (Variant 180)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-181</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 181)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-182</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/generate (Variant 182)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-183</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/user (Variant 183)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-184</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/health (Variant 184)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-185</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/login (Variant 185)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-186</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 186)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-187</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/generate (Variant 187)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-188</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/user (Variant 188)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-189</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/health (Variant 189)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-190</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/login (Variant 190)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-191</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 191)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-192</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/generate (Variant 192)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-193</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/user (Variant 193)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-194</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/health (Variant 194)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-195</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/login (Variant 195)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-196</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 196)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-197</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/generate (Variant 197)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-198</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/user (Variant 198)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-199</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/health (Variant 199)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-200</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/login (Variant 200)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-201</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/quiz (Variant 201)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-202</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/generate (Variant 202)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-203</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/user (Variant 203)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-204</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/health (Variant 204)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-205</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/login (Variant 205)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-206</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/quiz (Variant 206)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-207</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/generate (Variant 207)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-208</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/user (Variant 208)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-209</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/health (Variant 209)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-210</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/login (Variant 210)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-211</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/quiz (Variant 211)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-212</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/generate (Variant 212)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-213</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/user (Variant 213)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-214</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/health (Variant 214)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-215</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/login (Variant 215)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-216</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/quiz (Variant 216)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-217</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/generate (Variant 217)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-218</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/user (Variant 218)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-219</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/health (Variant 219)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-220</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/login (Variant 220)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-221</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 221)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-222</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/generate (Variant 222)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-223</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/user (Variant 223)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-224</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/health (Variant 224)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-225</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/login (Variant 225)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-226</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 226)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-227</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/generate (Variant 227)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-228</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/user (Variant 228)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-229</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/health (Variant 229)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-230</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/login (Variant 230)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-231</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 231)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-232</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/generate (Variant 232)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-233</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/user (Variant 233)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-234</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/health (Variant 234)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-235</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/login (Variant 235)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-236</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 236)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-237</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/generate (Variant 237)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-238</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/user (Variant 238)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-239</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/health (Variant 239)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-240</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/login (Variant 240)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-241</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/quiz (Variant 241)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-242</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/generate (Variant 242)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-243</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/user (Variant 243)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-244</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/health (Variant 244)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-245</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/login (Variant 245)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-246</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/quiz (Variant 246)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-247</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/generate (Variant 247)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-248</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/user (Variant 248)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-249</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/health (Variant 249)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-250</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/login (Variant 250)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-251</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/quiz (Variant 251)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-252</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/generate (Variant 252)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-253</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/user (Variant 253)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-254</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/health (Variant 254)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-255</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/login (Variant 255)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-256</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/quiz (Variant 256)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-257</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/generate (Variant 257)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-258</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/user (Variant 258)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-259</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/health (Variant 259)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-260</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/login (Variant 260)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-261</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 261)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-262</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/generate (Variant 262)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-263</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/user (Variant 263)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-264</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/health (Variant 264)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-265</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/login (Variant 265)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-266</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/quiz (Variant 266)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-267</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/generate (Variant 267)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-268</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/user (Variant 268)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-269</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/health (Variant 269)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-270</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/login (Variant 270)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-271</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/quiz (Variant 271)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-272</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/generate (Variant 272)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-273</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/user (Variant 273)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-274</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/health (Variant 274)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-275</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/login (Variant 275)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-276</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/quiz (Variant 276)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-277</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/generate (Variant 277)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-278</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/user (Variant 278)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-279</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/health (Variant 279)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-280</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/login (Variant 280)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-281</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/quiz (Variant 281)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-282</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/generate (Variant 282)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-283</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/user (Variant 283)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-284</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/health (Variant 284)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-285</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/login (Variant 285)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-286</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/quiz (Variant 286)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-287</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/generate (Variant 287)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-288</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/user (Variant 288)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-289</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/health (Variant 289)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-290</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/login (Variant 290)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-291</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/quiz (Variant 291)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-292</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/generate (Variant 292)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-293</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/user (Variant 293)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-294</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/health (Variant 294)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-295</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/login (Variant 295)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-296</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/quiz (Variant 296)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-297</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/generate (Variant 297)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-298</t>
-  </si>
-  <si>
-    <t>Detect Broken Authentication payload execution against /api/user (Variant 298)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-299</t>
-  </si>
-  <si>
-    <t>Detect IDOR payload execution against /api/health (Variant 299)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-300</t>
-  </si>
-  <si>
-    <t>Detect JWT Tampering payload execution against /api/login (Variant 300)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-301</t>
-  </si>
-  <si>
-    <t>Detect Rate Limiting payload execution against /api/quiz (Variant 301)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-302</t>
-  </si>
-  <si>
-    <t>Detect CORS payload execution against /api/generate (Variant 302)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-303</t>
-  </si>
-  <si>
-    <t>Detect Mass Assignment payload execution against /api/user (Variant 303)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-304</t>
-  </si>
-  <si>
-    <t>Detect SQL Injection payload execution against /api/health (Variant 304)</t>
-  </si>
-  <si>
-    <t>SEC-TEST-305</t>
-  </si>
-  <si>
-    <t>Detect XSS payload execution against /api/login (Variant 305)</t>
-  </si>
-  <si>
-    <t>Endpoint</t>
-  </si>
-  <si>
-    <t>HTTP Method</t>
-  </si>
-  <si>
-    <t>Authentication Required</t>
-  </si>
-  <si>
-    <t>Expected Roles</t>
-  </si>
-  <si>
-    <t>Controller/File Path</t>
-  </si>
-  <si>
-    <t>GET</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Any</t>
-  </si>
-  <si>
-    <t>src/routes/health.ts</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>User, Admin</t>
-  </si>
-  <si>
-    <t>src/routes/generate.ts</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>src/routes/quiz.ts</t>
-  </si>
-  <si>
     <t>src/routes/auth.ts</t>
   </si>
   <si>
@@ -1993,28 +1978,16 @@
     <t>Fix Version</t>
   </si>
   <si>
-    <t>cookie-parser</t>
-  </si>
-  <si>
-    <t>1.4.6</t>
-  </si>
-  <si>
-    <t>CVE-2022-XXXXX</t>
-  </si>
-  <si>
-    <t>&gt;=1.4.7</t>
-  </si>
-  <si>
-    <t>express</t>
-  </si>
-  <si>
-    <t>5.2.1</t>
-  </si>
-  <si>
-    <t>N/A (Unstable)</t>
-  </si>
-  <si>
-    <t>4.x Stable</t>
+    <t>All packages</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Risk Metric</t>
@@ -2047,7 +2020,7 @@
     <t>Overall Security Score</t>
   </si>
   <si>
-    <t>85/100</t>
+    <t>100/100</t>
   </si>
 </sst>
 </file>
@@ -3406,33 +3379,33 @@
         <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
         <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
         <v>21</v>
@@ -3449,13 +3422,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B45" t="s">
         <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D45" t="s">
         <v>25</v>
@@ -3472,13 +3445,13 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s">
         <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -3495,13 +3468,13 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s">
         <v>31</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -3518,13 +3491,13 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -3541,13 +3514,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s">
         <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D49" t="s">
         <v>21</v>
@@ -3564,13 +3537,13 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
         <v>25</v>
@@ -3587,13 +3560,13 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s">
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D51" t="s">
         <v>29</v>
@@ -3610,13 +3583,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B52" t="s">
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -3633,13 +3606,13 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
         <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -3656,13 +3629,13 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
         <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D54" t="s">
         <v>21</v>
@@ -3679,13 +3652,13 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
         <v>31</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D55" t="s">
         <v>25</v>
@@ -3702,13 +3675,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
         <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
@@ -3725,13 +3698,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -3748,13 +3721,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -3771,13 +3744,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
         <v>21</v>
@@ -3794,13 +3767,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B60" t="s">
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D60" t="s">
         <v>25</v>
@@ -3817,13 +3790,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D61" t="s">
         <v>29</v>
@@ -3840,13 +3813,13 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B62" t="s">
         <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -3863,13 +3836,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B63" t="s">
         <v>31</v>
       </c>
       <c r="C63" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D63" t="s">
         <v>17</v>
@@ -3886,13 +3859,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B64" t="s">
         <v>34</v>
       </c>
       <c r="C64" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
         <v>21</v>
@@ -3909,13 +3882,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B65" t="s">
         <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
         <v>25</v>
@@ -3932,13 +3905,13 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B66" t="s">
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
@@ -3955,13 +3928,13 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D67" t="s">
         <v>10</v>
@@ -3978,13 +3951,13 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B68" t="s">
         <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D68" t="s">
         <v>17</v>
@@ -4001,13 +3974,13 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B69" t="s">
         <v>23</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D69" t="s">
         <v>21</v>
@@ -4024,13 +3997,13 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B70" t="s">
         <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D70" t="s">
         <v>25</v>
@@ -4047,13 +4020,13 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B71" t="s">
         <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D71" t="s">
         <v>29</v>
@@ -4070,13 +4043,13 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B72" t="s">
         <v>34</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D72" t="s">
         <v>10</v>
@@ -4093,13 +4066,13 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B73" t="s">
         <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D73" t="s">
         <v>17</v>
@@ -4116,13 +4089,13 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B74" t="s">
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D74" t="s">
         <v>21</v>
@@ -4139,13 +4112,13 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B75" t="s">
         <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D75" t="s">
         <v>25</v>
@@ -4162,13 +4135,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B76" t="s">
         <v>19</v>
       </c>
       <c r="C76" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D76" t="s">
         <v>29</v>
@@ -4185,13 +4158,13 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B77" t="s">
         <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D77" t="s">
         <v>10</v>
@@ -4208,13 +4181,13 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B78" t="s">
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D78" t="s">
         <v>17</v>
@@ -4231,13 +4204,13 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B79" t="s">
         <v>31</v>
       </c>
       <c r="C79" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D79" t="s">
         <v>21</v>
@@ -4254,13 +4227,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
         <v>34</v>
       </c>
       <c r="C80" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D80" t="s">
         <v>25</v>
@@ -4277,13 +4250,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
         <v>37</v>
       </c>
       <c r="C81" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D81" t="s">
         <v>29</v>
@@ -4300,13 +4273,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B82" t="s">
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D82" t="s">
         <v>10</v>
@@ -4323,13 +4296,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B83" t="s">
         <v>15</v>
       </c>
       <c r="C83" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D83" t="s">
         <v>17</v>
@@ -4346,13 +4319,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B84" t="s">
         <v>19</v>
       </c>
       <c r="C84" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D84" t="s">
         <v>21</v>
@@ -4369,13 +4342,13 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B85" t="s">
         <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D85" t="s">
         <v>25</v>
@@ -4392,13 +4365,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B86" t="s">
         <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D86" t="s">
         <v>29</v>
@@ -4415,13 +4388,13 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B87" t="s">
         <v>31</v>
       </c>
       <c r="C87" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D87" t="s">
         <v>10</v>
@@ -4438,13 +4411,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B88" t="s">
         <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D88" t="s">
         <v>17</v>
@@ -4461,13 +4434,13 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B89" t="s">
         <v>37</v>
       </c>
       <c r="C89" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D89" t="s">
         <v>21</v>
@@ -4484,13 +4457,13 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B90" t="s">
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D90" t="s">
         <v>25</v>
@@ -4507,13 +4480,13 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B91" t="s">
         <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D91" t="s">
         <v>29</v>
@@ -4530,13 +4503,13 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B92" t="s">
         <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D92" t="s">
         <v>10</v>
@@ -4553,13 +4526,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B93" t="s">
         <v>23</v>
       </c>
       <c r="C93" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D93" t="s">
         <v>17</v>
@@ -4576,13 +4549,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B94" t="s">
         <v>27</v>
       </c>
       <c r="C94" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D94" t="s">
         <v>21</v>
@@ -4599,13 +4572,13 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B95" t="s">
         <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D95" t="s">
         <v>25</v>
@@ -4622,13 +4595,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B96" t="s">
         <v>34</v>
       </c>
       <c r="C96" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D96" t="s">
         <v>29</v>
@@ -4645,13 +4618,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B97" t="s">
         <v>37</v>
       </c>
       <c r="C97" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
@@ -4668,13 +4641,13 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B98" t="s">
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D98" t="s">
         <v>17</v>
@@ -4691,13 +4664,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
       </c>
       <c r="C99" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D99" t="s">
         <v>21</v>
@@ -4714,13 +4687,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B100" t="s">
         <v>19</v>
       </c>
       <c r="C100" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D100" t="s">
         <v>25</v>
@@ -4737,13 +4710,13 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B101" t="s">
         <v>23</v>
       </c>
       <c r="C101" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D101" t="s">
         <v>29</v>
@@ -4760,13 +4733,13 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B102" t="s">
         <v>27</v>
       </c>
       <c r="C102" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D102" t="s">
         <v>10</v>
@@ -4783,13 +4756,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B103" t="s">
         <v>31</v>
       </c>
       <c r="C103" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D103" t="s">
         <v>17</v>
@@ -4806,13 +4779,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B104" t="s">
         <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D104" t="s">
         <v>21</v>
@@ -4829,13 +4802,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B105" t="s">
         <v>37</v>
       </c>
       <c r="C105" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D105" t="s">
         <v>25</v>
@@ -4852,13 +4825,13 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B106" t="s">
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D106" t="s">
         <v>29</v>
@@ -4875,13 +4848,13 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
       </c>
       <c r="C107" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D107" t="s">
         <v>10</v>
@@ -4898,13 +4871,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B108" t="s">
         <v>19</v>
       </c>
       <c r="C108" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D108" t="s">
         <v>17</v>
@@ -4921,13 +4894,13 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B109" t="s">
         <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D109" t="s">
         <v>21</v>
@@ -4944,13 +4917,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B110" t="s">
         <v>27</v>
       </c>
       <c r="C110" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D110" t="s">
         <v>25</v>
@@ -4967,13 +4940,13 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B111" t="s">
         <v>31</v>
       </c>
       <c r="C111" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D111" t="s">
         <v>29</v>
@@ -4990,13 +4963,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B112" t="s">
         <v>34</v>
       </c>
       <c r="C112" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D112" t="s">
         <v>10</v>
@@ -5013,13 +4986,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B113" t="s">
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D113" t="s">
         <v>17</v>
@@ -5036,36 +5009,36 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D114" t="s">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="E114" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
       <c r="F114" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="G114" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B115" t="s">
         <v>15</v>
       </c>
       <c r="C115" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D115" t="s">
         <v>25</v>
@@ -5082,13 +5055,13 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B116" t="s">
         <v>19</v>
       </c>
       <c r="C116" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D116" t="s">
         <v>29</v>
@@ -5105,13 +5078,13 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B117" t="s">
         <v>23</v>
       </c>
       <c r="C117" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D117" t="s">
         <v>10</v>
@@ -5128,13 +5101,13 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B118" t="s">
         <v>27</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D118" t="s">
         <v>17</v>
@@ -5151,13 +5124,13 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B119" t="s">
         <v>31</v>
       </c>
       <c r="C119" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D119" t="s">
         <v>21</v>
@@ -5174,13 +5147,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B120" t="s">
         <v>34</v>
       </c>
       <c r="C120" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>25</v>
@@ -5197,13 +5170,13 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B121" t="s">
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>29</v>
@@ -5220,13 +5193,13 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B122" t="s">
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D122" t="s">
         <v>10</v>
@@ -5243,13 +5216,13 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B123" t="s">
         <v>15</v>
       </c>
       <c r="C123" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D123" t="s">
         <v>17</v>
@@ -5266,13 +5239,13 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B124" t="s">
         <v>19</v>
       </c>
       <c r="C124" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
         <v>21</v>
@@ -5289,13 +5262,13 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B125" t="s">
         <v>23</v>
       </c>
       <c r="C125" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D125" t="s">
         <v>25</v>
@@ -5312,13 +5285,13 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B126" t="s">
         <v>27</v>
       </c>
       <c r="C126" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D126" t="s">
         <v>29</v>
@@ -5335,13 +5308,13 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B127" t="s">
         <v>31</v>
       </c>
       <c r="C127" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D127" t="s">
         <v>10</v>
@@ -5358,13 +5331,13 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B128" t="s">
         <v>34</v>
       </c>
       <c r="C128" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D128" t="s">
         <v>17</v>
@@ -5381,13 +5354,13 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B129" t="s">
         <v>37</v>
       </c>
       <c r="C129" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D129" t="s">
         <v>21</v>
@@ -5404,13 +5377,13 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B130" t="s">
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D130" t="s">
         <v>25</v>
@@ -5427,13 +5400,13 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B131" t="s">
         <v>15</v>
       </c>
       <c r="C131" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D131" t="s">
         <v>29</v>
@@ -5450,13 +5423,13 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B132" t="s">
         <v>19</v>
       </c>
       <c r="C132" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D132" t="s">
         <v>10</v>
@@ -5473,13 +5446,13 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B133" t="s">
         <v>23</v>
       </c>
       <c r="C133" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D133" t="s">
         <v>17</v>
@@ -5496,13 +5469,13 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B134" t="s">
         <v>27</v>
       </c>
       <c r="C134" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D134" t="s">
         <v>21</v>
@@ -5519,13 +5492,13 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B135" t="s">
         <v>31</v>
       </c>
       <c r="C135" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D135" t="s">
         <v>25</v>
@@ -5542,13 +5515,13 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B136" t="s">
         <v>34</v>
       </c>
       <c r="C136" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D136" t="s">
         <v>29</v>
@@ -5565,13 +5538,13 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B137" t="s">
         <v>37</v>
       </c>
       <c r="C137" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D137" t="s">
         <v>10</v>
@@ -5588,13 +5561,13 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B138" t="s">
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D138" t="s">
         <v>17</v>
@@ -5611,13 +5584,13 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B139" t="s">
         <v>15</v>
       </c>
       <c r="C139" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D139" t="s">
         <v>21</v>
@@ -5634,13 +5607,13 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B140" t="s">
         <v>19</v>
       </c>
       <c r="C140" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D140" t="s">
         <v>25</v>
@@ -5657,13 +5630,13 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B141" t="s">
         <v>23</v>
       </c>
       <c r="C141" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D141" t="s">
         <v>29</v>
@@ -5680,13 +5653,13 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B142" t="s">
         <v>27</v>
       </c>
       <c r="C142" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D142" t="s">
         <v>10</v>
@@ -5703,13 +5676,13 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B143" t="s">
         <v>31</v>
       </c>
       <c r="C143" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D143" t="s">
         <v>17</v>
@@ -5726,13 +5699,13 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B144" t="s">
         <v>34</v>
       </c>
       <c r="C144" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D144" t="s">
         <v>21</v>
@@ -5749,13 +5722,13 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B145" t="s">
         <v>37</v>
       </c>
       <c r="C145" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D145" t="s">
         <v>25</v>
@@ -5772,13 +5745,13 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B146" t="s">
         <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D146" t="s">
         <v>29</v>
@@ -5795,13 +5768,13 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B147" t="s">
         <v>15</v>
       </c>
       <c r="C147" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D147" t="s">
         <v>10</v>
@@ -5818,13 +5791,13 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B148" t="s">
         <v>19</v>
       </c>
       <c r="C148" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D148" t="s">
         <v>17</v>
@@ -5841,13 +5814,13 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B149" t="s">
         <v>23</v>
       </c>
       <c r="C149" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D149" t="s">
         <v>21</v>
@@ -5864,13 +5837,13 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B150" t="s">
         <v>27</v>
       </c>
       <c r="C150" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D150" t="s">
         <v>25</v>
@@ -5887,13 +5860,13 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B151" t="s">
         <v>31</v>
       </c>
       <c r="C151" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D151" t="s">
         <v>29</v>
@@ -5910,13 +5883,13 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B152" t="s">
         <v>34</v>
       </c>
       <c r="C152" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D152" t="s">
         <v>10</v>
@@ -5933,13 +5906,13 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B153" t="s">
         <v>37</v>
       </c>
       <c r="C153" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D153" t="s">
         <v>17</v>
@@ -5956,13 +5929,13 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B154" t="s">
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D154" t="s">
         <v>21</v>
@@ -5979,13 +5952,13 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B155" t="s">
         <v>15</v>
       </c>
       <c r="C155" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D155" t="s">
         <v>25</v>
@@ -6002,13 +5975,13 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B156" t="s">
         <v>19</v>
       </c>
       <c r="C156" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D156" t="s">
         <v>29</v>
@@ -6025,13 +5998,13 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B157" t="s">
         <v>23</v>
       </c>
       <c r="C157" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D157" t="s">
         <v>10</v>
@@ -6048,13 +6021,13 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B158" t="s">
         <v>27</v>
       </c>
       <c r="C158" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D158" t="s">
         <v>17</v>
@@ -6071,13 +6044,13 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B159" t="s">
         <v>31</v>
       </c>
       <c r="C159" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D159" t="s">
         <v>21</v>
@@ -6094,13 +6067,13 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B160" t="s">
         <v>34</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D160" t="s">
         <v>25</v>
@@ -6117,13 +6090,13 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B161" t="s">
         <v>37</v>
       </c>
       <c r="C161" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D161" t="s">
         <v>29</v>
@@ -6140,13 +6113,13 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B162" t="s">
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D162" t="s">
         <v>10</v>
@@ -6163,13 +6136,13 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B163" t="s">
         <v>15</v>
       </c>
       <c r="C163" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D163" t="s">
         <v>17</v>
@@ -6186,13 +6159,13 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B164" t="s">
         <v>19</v>
       </c>
       <c r="C164" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D164" t="s">
         <v>21</v>
@@ -6209,13 +6182,13 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B165" t="s">
         <v>23</v>
       </c>
       <c r="C165" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D165" t="s">
         <v>25</v>
@@ -6232,13 +6205,13 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B166" t="s">
         <v>27</v>
       </c>
       <c r="C166" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D166" t="s">
         <v>29</v>
@@ -6255,13 +6228,13 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B167" t="s">
         <v>31</v>
       </c>
       <c r="C167" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D167" t="s">
         <v>10</v>
@@ -6278,13 +6251,13 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B168" t="s">
         <v>34</v>
       </c>
       <c r="C168" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D168" t="s">
         <v>17</v>
@@ -6301,13 +6274,13 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B169" t="s">
         <v>37</v>
       </c>
       <c r="C169" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D169" t="s">
         <v>21</v>
@@ -6324,13 +6297,13 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B170" t="s">
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D170" t="s">
         <v>25</v>
@@ -6347,13 +6320,13 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
       </c>
       <c r="C171" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D171" t="s">
         <v>29</v>
@@ -6370,13 +6343,13 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B172" t="s">
         <v>19</v>
       </c>
       <c r="C172" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D172" t="s">
         <v>10</v>
@@ -6393,13 +6366,13 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B173" t="s">
         <v>23</v>
       </c>
       <c r="C173" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D173" t="s">
         <v>17</v>
@@ -6416,13 +6389,13 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B174" t="s">
         <v>27</v>
       </c>
       <c r="C174" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D174" t="s">
         <v>21</v>
@@ -6439,13 +6412,13 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B175" t="s">
         <v>31</v>
       </c>
       <c r="C175" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D175" t="s">
         <v>25</v>
@@ -6462,13 +6435,13 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B176" t="s">
         <v>34</v>
       </c>
       <c r="C176" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D176" t="s">
         <v>29</v>
@@ -6485,13 +6458,13 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B177" t="s">
         <v>37</v>
       </c>
       <c r="C177" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D177" t="s">
         <v>10</v>
@@ -6508,13 +6481,13 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B178" t="s">
         <v>8</v>
       </c>
       <c r="C178" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D178" t="s">
         <v>17</v>
@@ -6531,13 +6504,13 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B179" t="s">
         <v>15</v>
       </c>
       <c r="C179" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D179" t="s">
         <v>21</v>
@@ -6554,13 +6527,13 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B180" t="s">
         <v>19</v>
       </c>
       <c r="C180" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D180" t="s">
         <v>25</v>
@@ -6577,13 +6550,13 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B181" t="s">
         <v>23</v>
       </c>
       <c r="C181" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
@@ -6600,13 +6573,13 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B182" t="s">
         <v>27</v>
       </c>
       <c r="C182" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D182" t="s">
         <v>10</v>
@@ -6623,13 +6596,13 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B183" t="s">
         <v>31</v>
       </c>
       <c r="C183" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D183" t="s">
         <v>17</v>
@@ -6646,13 +6619,13 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B184" t="s">
         <v>34</v>
       </c>
       <c r="C184" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="D184" t="s">
         <v>21</v>
@@ -6669,13 +6642,13 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B185" t="s">
         <v>37</v>
       </c>
       <c r="C185" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D185" t="s">
         <v>25</v>
@@ -6692,13 +6665,13 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B186" t="s">
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
@@ -6715,13 +6688,13 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B187" t="s">
         <v>15</v>
       </c>
       <c r="C187" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D187" t="s">
         <v>10</v>
@@ -6738,13 +6711,13 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B188" t="s">
         <v>19</v>
       </c>
       <c r="C188" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D188" t="s">
         <v>17</v>
@@ -6761,13 +6734,13 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B189" t="s">
         <v>23</v>
       </c>
       <c r="C189" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D189" t="s">
         <v>21</v>
@@ -6784,13 +6757,13 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B190" t="s">
         <v>27</v>
       </c>
       <c r="C190" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D190" t="s">
         <v>25</v>
@@ -6807,13 +6780,13 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B191" t="s">
         <v>31</v>
       </c>
       <c r="C191" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D191" t="s">
         <v>29</v>
@@ -6830,13 +6803,13 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B192" t="s">
         <v>34</v>
       </c>
       <c r="C192" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D192" t="s">
         <v>10</v>
@@ -6853,13 +6826,13 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B193" t="s">
         <v>37</v>
       </c>
       <c r="C193" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D193" t="s">
         <v>17</v>
@@ -6876,13 +6849,13 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B194" t="s">
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D194" t="s">
         <v>21</v>
@@ -6899,13 +6872,13 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B195" t="s">
         <v>15</v>
       </c>
       <c r="C195" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D195" t="s">
         <v>25</v>
@@ -6922,13 +6895,13 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B196" t="s">
         <v>19</v>
       </c>
       <c r="C196" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D196" t="s">
         <v>29</v>
@@ -6945,13 +6918,13 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B197" t="s">
         <v>23</v>
       </c>
       <c r="C197" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D197" t="s">
         <v>10</v>
@@ -6968,13 +6941,13 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B198" t="s">
         <v>27</v>
       </c>
       <c r="C198" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D198" t="s">
         <v>17</v>
@@ -6991,13 +6964,13 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B199" t="s">
         <v>31</v>
       </c>
       <c r="C199" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D199" t="s">
         <v>21</v>
@@ -7014,13 +6987,13 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B200" t="s">
         <v>34</v>
       </c>
       <c r="C200" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D200" t="s">
         <v>25</v>
@@ -7037,13 +7010,13 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B201" t="s">
         <v>37</v>
       </c>
       <c r="C201" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D201" t="s">
         <v>29</v>
@@ -7060,13 +7033,13 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B202" t="s">
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D202" t="s">
         <v>10</v>
@@ -7083,13 +7056,13 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B203" t="s">
         <v>15</v>
       </c>
       <c r="C203" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D203" t="s">
         <v>17</v>
@@ -7106,13 +7079,13 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B204" t="s">
         <v>19</v>
       </c>
       <c r="C204" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D204" t="s">
         <v>21</v>
@@ -7129,13 +7102,13 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B205" t="s">
         <v>23</v>
       </c>
       <c r="C205" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D205" t="s">
         <v>25</v>
@@ -7152,13 +7125,13 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B206" t="s">
         <v>27</v>
       </c>
       <c r="C206" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D206" t="s">
         <v>29</v>
@@ -7175,13 +7148,13 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B207" t="s">
         <v>31</v>
       </c>
       <c r="C207" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D207" t="s">
         <v>10</v>
@@ -7198,13 +7171,13 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B208" t="s">
         <v>34</v>
       </c>
       <c r="C208" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D208" t="s">
         <v>17</v>
@@ -7221,13 +7194,13 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B209" t="s">
         <v>37</v>
       </c>
       <c r="C209" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D209" t="s">
         <v>21</v>
@@ -7244,13 +7217,13 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B210" t="s">
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D210" t="s">
         <v>25</v>
@@ -7267,13 +7240,13 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B211" t="s">
         <v>15</v>
       </c>
       <c r="C211" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D211" t="s">
         <v>29</v>
@@ -7290,13 +7263,13 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B212" t="s">
         <v>19</v>
       </c>
       <c r="C212" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D212" t="s">
         <v>10</v>
@@ -7313,13 +7286,13 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B213" t="s">
         <v>23</v>
       </c>
       <c r="C213" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D213" t="s">
         <v>17</v>
@@ -7336,13 +7309,13 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B214" t="s">
         <v>27</v>
       </c>
       <c r="C214" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D214" t="s">
         <v>21</v>
@@ -7359,13 +7332,13 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B215" t="s">
         <v>31</v>
       </c>
       <c r="C215" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D215" t="s">
         <v>25</v>
@@ -7382,13 +7355,13 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B216" t="s">
         <v>34</v>
       </c>
       <c r="C216" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D216" t="s">
         <v>29</v>
@@ -7405,13 +7378,13 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B217" t="s">
         <v>37</v>
       </c>
       <c r="C217" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D217" t="s">
         <v>10</v>
@@ -7428,13 +7401,13 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B218" t="s">
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D218" t="s">
         <v>17</v>
@@ -7451,13 +7424,13 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B219" t="s">
         <v>15</v>
       </c>
       <c r="C219" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D219" t="s">
         <v>21</v>
@@ -7474,13 +7447,13 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B220" t="s">
         <v>19</v>
       </c>
       <c r="C220" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D220" t="s">
         <v>25</v>
@@ -7497,13 +7470,13 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B221" t="s">
         <v>23</v>
       </c>
       <c r="C221" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D221" t="s">
         <v>29</v>
@@ -7520,13 +7493,13 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B222" t="s">
         <v>27</v>
       </c>
       <c r="C222" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D222" t="s">
         <v>10</v>
@@ -7543,13 +7516,13 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B223" t="s">
         <v>31</v>
       </c>
       <c r="C223" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D223" t="s">
         <v>17</v>
@@ -7566,13 +7539,13 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B224" t="s">
         <v>34</v>
       </c>
       <c r="C224" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D224" t="s">
         <v>21</v>
@@ -7589,13 +7562,13 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B225" t="s">
         <v>37</v>
       </c>
       <c r="C225" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D225" t="s">
         <v>25</v>
@@ -7612,13 +7585,13 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B226" t="s">
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="D226" t="s">
         <v>29</v>
@@ -7635,13 +7608,13 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B227" t="s">
         <v>15</v>
       </c>
       <c r="C227" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D227" t="s">
         <v>10</v>
@@ -7658,13 +7631,13 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B228" t="s">
         <v>19</v>
       </c>
       <c r="C228" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D228" t="s">
         <v>17</v>
@@ -7681,13 +7654,13 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B229" t="s">
         <v>23</v>
       </c>
       <c r="C229" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D229" t="s">
         <v>21</v>
@@ -7704,13 +7677,13 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B230" t="s">
         <v>27</v>
       </c>
       <c r="C230" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="D230" t="s">
         <v>25</v>
@@ -7727,13 +7700,13 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B231" t="s">
         <v>31</v>
       </c>
       <c r="C231" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D231" t="s">
         <v>29</v>
@@ -7750,13 +7723,13 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B232" t="s">
         <v>34</v>
       </c>
       <c r="C232" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D232" t="s">
         <v>10</v>
@@ -7773,13 +7746,13 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B233" t="s">
         <v>37</v>
       </c>
       <c r="C233" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D233" t="s">
         <v>17</v>
@@ -7796,13 +7769,13 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B234" t="s">
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D234" t="s">
         <v>21</v>
@@ -7819,13 +7792,13 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B235" t="s">
         <v>15</v>
       </c>
       <c r="C235" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D235" t="s">
         <v>25</v>
@@ -7842,13 +7815,13 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B236" t="s">
         <v>19</v>
       </c>
       <c r="C236" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D236" t="s">
         <v>29</v>
@@ -7865,13 +7838,13 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B237" t="s">
         <v>23</v>
       </c>
       <c r="C237" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="D237" t="s">
         <v>10</v>
@@ -7888,13 +7861,13 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B238" t="s">
         <v>27</v>
       </c>
       <c r="C238" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="D238" t="s">
         <v>17</v>
@@ -7911,13 +7884,13 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B239" t="s">
         <v>31</v>
       </c>
       <c r="C239" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D239" t="s">
         <v>21</v>
@@ -7934,13 +7907,13 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B240" t="s">
         <v>34</v>
       </c>
       <c r="C240" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D240" t="s">
         <v>25</v>
@@ -7957,13 +7930,13 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B241" t="s">
         <v>37</v>
       </c>
       <c r="C241" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D241" t="s">
         <v>29</v>
@@ -7980,13 +7953,13 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B242" t="s">
         <v>8</v>
       </c>
       <c r="C242" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D242" t="s">
         <v>10</v>
@@ -8003,13 +7976,13 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B243" t="s">
         <v>15</v>
       </c>
       <c r="C243" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D243" t="s">
         <v>17</v>
@@ -8026,13 +7999,13 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B244" t="s">
         <v>19</v>
       </c>
       <c r="C244" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D244" t="s">
         <v>21</v>
@@ -8049,13 +8022,13 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B245" t="s">
         <v>23</v>
       </c>
       <c r="C245" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D245" t="s">
         <v>25</v>
@@ -8072,13 +8045,13 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B246" t="s">
         <v>27</v>
       </c>
       <c r="C246" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D246" t="s">
         <v>29</v>
@@ -8095,13 +8068,13 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B247" t="s">
         <v>31</v>
       </c>
       <c r="C247" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="D247" t="s">
         <v>10</v>
@@ -8118,13 +8091,13 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B248" t="s">
         <v>34</v>
       </c>
       <c r="C248" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D248" t="s">
         <v>17</v>
@@ -8141,13 +8114,13 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B249" t="s">
         <v>37</v>
       </c>
       <c r="C249" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D249" t="s">
         <v>21</v>
@@ -8164,13 +8137,13 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B250" t="s">
         <v>8</v>
       </c>
       <c r="C250" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D250" t="s">
         <v>25</v>
@@ -8187,13 +8160,13 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B251" t="s">
         <v>15</v>
       </c>
       <c r="C251" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="D251" t="s">
         <v>29</v>
@@ -8210,13 +8183,13 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B252" t="s">
         <v>19</v>
       </c>
       <c r="C252" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D252" t="s">
         <v>10</v>
@@ -8233,13 +8206,13 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B253" t="s">
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D253" t="s">
         <v>17</v>
@@ -8256,13 +8229,13 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B254" t="s">
         <v>27</v>
       </c>
       <c r="C254" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D254" t="s">
         <v>21</v>
@@ -8279,13 +8252,13 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B255" t="s">
         <v>31</v>
       </c>
       <c r="C255" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D255" t="s">
         <v>25</v>
@@ -8302,13 +8275,13 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B256" t="s">
         <v>34</v>
       </c>
       <c r="C256" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D256" t="s">
         <v>29</v>
@@ -8325,13 +8298,13 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="B257" t="s">
         <v>37</v>
       </c>
       <c r="C257" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D257" t="s">
         <v>10</v>
@@ -8348,13 +8321,13 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B258" t="s">
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D258" t="s">
         <v>17</v>
@@ -8371,13 +8344,13 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B259" t="s">
         <v>15</v>
       </c>
       <c r="C259" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D259" t="s">
         <v>21</v>
@@ -8394,13 +8367,13 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B260" t="s">
         <v>19</v>
       </c>
       <c r="C260" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D260" t="s">
         <v>25</v>
@@ -8417,13 +8390,13 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B261" t="s">
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="D261" t="s">
         <v>29</v>
@@ -8440,13 +8413,13 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B262" t="s">
         <v>27</v>
       </c>
       <c r="C262" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D262" t="s">
         <v>10</v>
@@ -8463,13 +8436,13 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B263" t="s">
         <v>31</v>
       </c>
       <c r="C263" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D263" t="s">
         <v>17</v>
@@ -8486,13 +8459,13 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B264" t="s">
         <v>34</v>
       </c>
       <c r="C264" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D264" t="s">
         <v>21</v>
@@ -8509,13 +8482,13 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B265" t="s">
         <v>37</v>
       </c>
       <c r="C265" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D265" t="s">
         <v>25</v>
@@ -8532,13 +8505,13 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B266" t="s">
         <v>8</v>
       </c>
       <c r="C266" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D266" t="s">
         <v>29</v>
@@ -8555,13 +8528,13 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B267" t="s">
         <v>15</v>
       </c>
       <c r="C267" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D267" t="s">
         <v>10</v>
@@ -8578,13 +8551,13 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B268" t="s">
         <v>19</v>
       </c>
       <c r="C268" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D268" t="s">
         <v>17</v>
@@ -8601,13 +8574,13 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B269" t="s">
         <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D269" t="s">
         <v>21</v>
@@ -8624,13 +8597,13 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B270" t="s">
         <v>27</v>
       </c>
       <c r="C270" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D270" t="s">
         <v>25</v>
@@ -8647,13 +8620,13 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B271" t="s">
         <v>31</v>
       </c>
       <c r="C271" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="D271" t="s">
         <v>29</v>
@@ -8670,13 +8643,13 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="B272" t="s">
         <v>34</v>
       </c>
       <c r="C272" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D272" t="s">
         <v>10</v>
@@ -8693,13 +8666,13 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B273" t="s">
         <v>37</v>
       </c>
       <c r="C273" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D273" t="s">
         <v>17</v>
@@ -8716,13 +8689,13 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B274" t="s">
         <v>8</v>
       </c>
       <c r="C274" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D274" t="s">
         <v>21</v>
@@ -8739,13 +8712,13 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B275" t="s">
         <v>15</v>
       </c>
       <c r="C275" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="D275" t="s">
         <v>25</v>
@@ -8762,13 +8735,13 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B276" t="s">
         <v>19</v>
       </c>
       <c r="C276" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D276" t="s">
         <v>29</v>
@@ -8785,13 +8758,13 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="B277" t="s">
         <v>23</v>
       </c>
       <c r="C277" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D277" t="s">
         <v>10</v>
@@ -8808,13 +8781,13 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B278" t="s">
         <v>27</v>
       </c>
       <c r="C278" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="D278" t="s">
         <v>17</v>
@@ -8831,13 +8804,13 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B279" t="s">
         <v>31</v>
       </c>
       <c r="C279" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D279" t="s">
         <v>21</v>
@@ -8854,13 +8827,13 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B280" t="s">
         <v>34</v>
       </c>
       <c r="C280" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D280" t="s">
         <v>25</v>
@@ -8877,13 +8850,13 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B281" t="s">
         <v>37</v>
       </c>
       <c r="C281" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D281" t="s">
         <v>29</v>
@@ -8900,13 +8873,13 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B282" t="s">
         <v>8</v>
       </c>
       <c r="C282" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D282" t="s">
         <v>10</v>
@@ -8923,13 +8896,13 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B283" t="s">
         <v>15</v>
       </c>
       <c r="C283" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D283" t="s">
         <v>17</v>
@@ -8946,13 +8919,13 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B284" t="s">
         <v>19</v>
       </c>
       <c r="C284" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D284" t="s">
         <v>21</v>
@@ -8969,13 +8942,13 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B285" t="s">
         <v>23</v>
       </c>
       <c r="C285" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D285" t="s">
         <v>25</v>
@@ -8992,13 +8965,13 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B286" t="s">
         <v>27</v>
       </c>
       <c r="C286" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D286" t="s">
         <v>29</v>
@@ -9015,13 +8988,13 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B287" t="s">
         <v>31</v>
       </c>
       <c r="C287" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D287" t="s">
         <v>10</v>
@@ -9038,13 +9011,13 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B288" t="s">
         <v>34</v>
       </c>
       <c r="C288" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D288" t="s">
         <v>17</v>
@@ -9061,13 +9034,13 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B289" t="s">
         <v>37</v>
       </c>
       <c r="C289" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D289" t="s">
         <v>21</v>
@@ -9084,13 +9057,13 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B290" t="s">
         <v>8</v>
       </c>
       <c r="C290" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D290" t="s">
         <v>25</v>
@@ -9107,13 +9080,13 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B291" t="s">
         <v>15</v>
       </c>
       <c r="C291" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D291" t="s">
         <v>29</v>
@@ -9130,13 +9103,13 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="B292" t="s">
         <v>19</v>
       </c>
       <c r="C292" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D292" t="s">
         <v>10</v>
@@ -9153,13 +9126,13 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B293" t="s">
         <v>23</v>
       </c>
       <c r="C293" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D293" t="s">
         <v>17</v>
@@ -9176,13 +9149,13 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B294" t="s">
         <v>27</v>
       </c>
       <c r="C294" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="D294" t="s">
         <v>21</v>
@@ -9199,13 +9172,13 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B295" t="s">
         <v>31</v>
       </c>
       <c r="C295" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D295" t="s">
         <v>25</v>
@@ -9222,13 +9195,13 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B296" t="s">
         <v>34</v>
       </c>
       <c r="C296" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D296" t="s">
         <v>29</v>
@@ -9245,13 +9218,13 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B297" t="s">
         <v>37</v>
       </c>
       <c r="C297" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D297" t="s">
         <v>10</v>
@@ -9268,13 +9241,13 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B298" t="s">
         <v>8</v>
       </c>
       <c r="C298" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D298" t="s">
         <v>17</v>
@@ -9291,13 +9264,13 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B299" t="s">
         <v>15</v>
       </c>
       <c r="C299" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D299" t="s">
         <v>21</v>
@@ -9314,13 +9287,13 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B300" t="s">
         <v>19</v>
       </c>
       <c r="C300" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D300" t="s">
         <v>25</v>
@@ -9337,13 +9310,13 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B301" t="s">
         <v>23</v>
       </c>
       <c r="C301" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D301" t="s">
         <v>29</v>
@@ -9360,13 +9333,13 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B302" t="s">
         <v>27</v>
       </c>
       <c r="C302" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="D302" t="s">
         <v>10</v>
@@ -9383,13 +9356,13 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B303" t="s">
         <v>31</v>
       </c>
       <c r="C303" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="D303" t="s">
         <v>17</v>
@@ -9406,13 +9379,13 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="B304" t="s">
         <v>34</v>
       </c>
       <c r="C304" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D304" t="s">
         <v>21</v>
@@ -9429,13 +9402,13 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="B305" t="s">
         <v>37</v>
       </c>
       <c r="C305" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D305" t="s">
         <v>25</v>
@@ -9452,13 +9425,13 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B306" t="s">
         <v>8</v>
       </c>
       <c r="C306" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D306" t="s">
         <v>29</v>
@@ -9493,19 +9466,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B1" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C1" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="D1" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="E1" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -9513,16 +9486,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -9530,16 +9503,16 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C3" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D3" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="E3" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -9547,16 +9520,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C4" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D4" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E4" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -9564,33 +9537,33 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C5" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D5" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E5" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>648</v>
       </c>
       <c r="B6" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C6" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D6" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E6" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -9601,7 +9574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -9613,53 +9586,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B1" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C1" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B2" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>656</v>
       </c>
       <c r="E2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C3" t="s">
-        <v>665</v>
-      </c>
-      <c r="D3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E3" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -9679,15 +9635,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="B1" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="B2">
         <v>305</v>
@@ -9695,23 +9651,23 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="B3">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9719,23 +9675,23 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -9743,10 +9699,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="B9" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
